--- a/All_Code/Q2_yy/Results/Tables/monthly_metrics.xlsx
+++ b/All_Code/Q2_yy/Results/Tables/monthly_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monthly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="monthly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,25 +517,25 @@
         <v>0.0607902335174163</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002984061041362153</v>
+        <v>0.00408686639893707</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07157883500948892</v>
+        <v>0.053386927185382</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03563440737791489</v>
+        <v>0.05988955031477539</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1244868.382182626</v>
+        <v>1225508.040250662</v>
       </c>
       <c r="K2" t="n">
-        <v>37559.57118000673</v>
+        <v>46749.86104991883</v>
       </c>
       <c r="L2" t="n">
-        <v>1282427.953362633</v>
+        <v>1272257.90130058</v>
       </c>
       <c r="M2" t="n">
         <v>28</v>
@@ -561,25 +561,25 @@
         <v>0.0741766860028585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004869097929143518</v>
+        <v>0.007147712684435968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07212192601168632</v>
+        <v>0.05379719439675463</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08187654816215137</v>
+        <v>0.09929204615211375</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1140975.578018611</v>
+        <v>1136410.838015093</v>
       </c>
       <c r="K3" t="n">
-        <v>65770.60013612256</v>
+        <v>85855.64563522166</v>
       </c>
       <c r="L3" t="n">
-        <v>1206746.178154733</v>
+        <v>1222266.483650314</v>
       </c>
       <c r="M3" t="n">
         <v>31</v>
@@ -605,25 +605,25 @@
         <v>0.06855424118724721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004198709440136662</v>
+        <v>0.006300489715047593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06250321013978596</v>
+        <v>0.05327931861317844</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1181395883587757</v>
+        <v>0.1244778854786405</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>951335.4713224963</v>
+        <v>952597.791863721</v>
       </c>
       <c r="K4" t="n">
-        <v>59966.56830190673</v>
+        <v>73693.90297309146</v>
       </c>
       <c r="L4" t="n">
-        <v>1011302.039624403</v>
+        <v>1026291.694836812</v>
       </c>
       <c r="M4" t="n">
         <v>30</v>
@@ -649,25 +649,25 @@
         <v>0.0680067534059391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003889228585893862</v>
+        <v>0.005251383179618364</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08718956590369931</v>
+        <v>0.07109688617899709</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1260976916842471</v>
+        <v>0.136501107545848</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1001258.808931265</v>
+        <v>1007758.888319433</v>
       </c>
       <c r="K5" t="n">
-        <v>53693.68881983489</v>
+        <v>66343.6932021278</v>
       </c>
       <c r="L5" t="n">
-        <v>1054952.4977511</v>
+        <v>1074102.581521562</v>
       </c>
       <c r="M5" t="n">
         <v>31</v>
@@ -693,25 +693,25 @@
         <v>0.0863453580021853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006361000198471713</v>
+        <v>0.008099732867319957</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1263767857338413</v>
+        <v>0.09263693300799701</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05532097970219259</v>
+        <v>0.09910190300318014</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1371330.26375037</v>
+        <v>1381579.637615665</v>
       </c>
       <c r="K6" t="n">
-        <v>96672.12592457606</v>
+        <v>108047.1279389527</v>
       </c>
       <c r="L6" t="n">
-        <v>1468002.389674946</v>
+        <v>1489626.765554617</v>
       </c>
       <c r="M6" t="n">
         <v>30</v>
@@ -737,25 +737,25 @@
         <v>0.07056216465958839</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005386646828486504</v>
+        <v>0.00659592753957691</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1052057406818513</v>
+        <v>0.08189208114944117</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05918912030134484</v>
+        <v>0.08621895087083639</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1508786.766900865</v>
+        <v>1516630.293227738</v>
       </c>
       <c r="K7" t="n">
-        <v>87487.18475002766</v>
+        <v>100238.2881361106</v>
       </c>
       <c r="L7" t="n">
-        <v>1596273.951650892</v>
+        <v>1616868.581363849</v>
       </c>
       <c r="M7" t="n">
         <v>31</v>
@@ -781,25 +781,25 @@
         <v>0.0678158437112128</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004850228172834132</v>
+        <v>0.006683207184304488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06734110771774893</v>
+        <v>0.05916817417036704</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1163150736847579</v>
+        <v>0.1243033817611687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1283379.669342721</v>
+        <v>1288573.515115956</v>
       </c>
       <c r="K8" t="n">
-        <v>78199.69507640283</v>
+        <v>95824.50293697616</v>
       </c>
       <c r="L8" t="n">
-        <v>1361579.364419124</v>
+        <v>1384398.018052933</v>
       </c>
       <c r="M8" t="n">
         <v>31</v>
@@ -825,25 +825,25 @@
         <v>0.06647836005947939</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004505360972691911</v>
+        <v>0.006347286485226886</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08206836217940627</v>
+        <v>0.07184268562225142</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1154513348105029</v>
+        <v>0.1249285752209407</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1143709.389427005</v>
+        <v>1149307.499705597</v>
       </c>
       <c r="K9" t="n">
-        <v>62626.99530077806</v>
+        <v>80416.18577771945</v>
       </c>
       <c r="L9" t="n">
-        <v>1206336.384727783</v>
+        <v>1229723.685483317</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
@@ -869,25 +869,25 @@
         <v>0.0585458955692973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002107143344413807</v>
+        <v>0.003203632302702284</v>
       </c>
       <c r="G10" t="n">
-        <v>0.103078481557899</v>
+        <v>0.09482307301631855</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1206799442434439</v>
+        <v>0.1231895495174353</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1251448.117507227</v>
+        <v>1237684.715904378</v>
       </c>
       <c r="K10" t="n">
-        <v>29151.34383387711</v>
+        <v>39403.23134142067</v>
       </c>
       <c r="L10" t="n">
-        <v>1280599.461341104</v>
+        <v>1277087.947245799</v>
       </c>
       <c r="M10" t="n">
         <v>31</v>
@@ -913,25 +913,25 @@
         <v>0.0477323857748148</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002855992674282402</v>
+        <v>0.003973011850905733</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0692091316584024</v>
+        <v>0.05258459797091785</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04458069297989268</v>
+        <v>0.06956901878322934</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1342811.221141556</v>
+        <v>1304649.639286321</v>
       </c>
       <c r="K11" t="n">
-        <v>35315.83468168988</v>
+        <v>43818.59342139595</v>
       </c>
       <c r="L11" t="n">
-        <v>1378127.055823246</v>
+        <v>1348468.232707717</v>
       </c>
       <c r="M11" t="n">
         <v>30</v>
@@ -957,25 +957,25 @@
         <v>0.0515964951713247</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005207082342073199</v>
+        <v>0.006349812424515167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06745457716330423</v>
+        <v>0.05591759134162844</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01269677234416531</v>
+        <v>0.04054466082433865</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1711467.285741909</v>
+        <v>1684311.763255575</v>
       </c>
       <c r="K12" t="n">
-        <v>75940.09038756505</v>
+        <v>83559.83948263353</v>
       </c>
       <c r="L12" t="n">
-        <v>1787407.376129474</v>
+        <v>1767871.602738209</v>
       </c>
       <c r="M12" t="n">
         <v>31</v>
